--- a/VALIDA (1).xlsx
+++ b/VALIDA (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beca\OneDrive\Escritorio\LOLIUM 2026\VALIDA LARTIGAU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BE2D83-ECF9-4B24-BD59-60B40F1F9F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D4BEBA-0C1F-4B67-9B6F-187E3F1F92AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,12 +54,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -89,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -108,6 +114,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,13 +399,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,7 +413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>46072</v>
       </c>
@@ -410,7 +421,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>46077</v>
       </c>
@@ -418,7 +429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>46087</v>
       </c>
@@ -426,7 +437,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>46101</v>
       </c>
@@ -434,7 +445,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>46121</v>
       </c>
@@ -442,7 +453,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>46136</v>
       </c>
@@ -450,7 +461,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>46154</v>
       </c>
@@ -458,7 +469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>46169</v>
       </c>
@@ -466,7 +477,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>46190</v>
       </c>
@@ -474,7 +485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>46206</v>
       </c>
@@ -482,17 +493,44 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>46219</v>
+      </c>
+      <c r="B12">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>46234</v>
+      </c>
+      <c r="B13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>46249</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0</v>
+      </c>
+      <c r="C14" s="11"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>46264</v>
+      </c>
+      <c r="B15" s="11">
+        <v>0</v>
+      </c>
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
